--- a/examples/AER25-125_BackEnd-_Endpoint_Submit_Excel_File_Quotations_Events.xlsx
+++ b/examples/AER25-125_BackEnd-_Endpoint_Submit_Excel_File_Quotations_Events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jgallardo\OneDrive - ACCION POINT SA\Escritorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF3F1BCD-3C35-4908-BD58-989C97550258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BCA3B9F-4E4C-4147-93A4-31482A761456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,247 +35,247 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="81">
   <si>
-    <t>Prioridad</t>
-  </si>
-  <si>
-    <t>ID CP</t>
-  </si>
-  <si>
-    <t>Título</t>
-  </si>
-  <si>
-    <t>Precondición</t>
-  </si>
-  <si>
-    <t>Validación Esperada</t>
-  </si>
-  <si>
-    <t>Resultado Obtenido</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
     <t>AER25-125: CP1</t>
   </si>
   <si>
-    <t>Validar carga exitosa con archivo .XLSX válido (nueva revisión)</t>
-  </si>
-  <si>
-    <t>Archivo Excel válido, revision="-1"</t>
-  </si>
-  <si>
-    <t>201/200, Mensaje: "Carga exitosa"</t>
-  </si>
-  <si>
     <t>AER25-125: CP2</t>
   </si>
   <si>
-    <t>Validar carga exitosa con archivo .XLSX válido (revisión existente)</t>
-  </si>
-  <si>
-    <t>Archivo Excel válido, revisión existente válida</t>
-  </si>
-  <si>
-    <t>201/200, registros existentes eliminados, nuevos insertados, mensaje: "Carga exitosa"</t>
-  </si>
-  <si>
     <t>AER25-125: CP3</t>
   </si>
   <si>
-    <t>Validar respuesta de error por formato de archivo inválido (ej. .CSV, .XLS, .TXT)</t>
-  </si>
-  <si>
-    <t>Tipo de archivo inválido, ej. .csv</t>
-  </si>
-  <si>
-    <t>400/415, Mensaje error: "Tipo de archivo no válido; sólo se permite .XLSX"</t>
-  </si>
-  <si>
     <t>AER25-125: CP4</t>
   </si>
   <si>
-    <t>Validar archivo con error de formato numérico en una fila</t>
-  </si>
-  <si>
-    <t>Archivo con valor numérico inválido en columna</t>
-  </si>
-  <si>
-    <t>400, Mensaje: "Error en fila X, columna 'Y': formato inválido"; BD NO modificada/rollback</t>
-  </si>
-  <si>
     <t>AER25-125: CP5</t>
   </si>
   <si>
-    <t>Validar archivo con error de formato de fecha en una fila</t>
-  </si>
-  <si>
-    <t>Archivo con valor de fecha inválido</t>
-  </si>
-  <si>
-    <t>400, "Error en fila X, columna 'Z': formato inválido"; Sin cambios en BD/rollback</t>
-  </si>
-  <si>
     <t>AER25-125: CP6</t>
   </si>
   <si>
-    <t>Validar rollback completo cuando ocurre un solo error en el archivo</t>
-  </si>
-  <si>
-    <t>Archivo contiene filas correctas y 1 fila errónea</t>
-  </si>
-  <si>
-    <t>400, BD sin cambios/rollback; mensaje de error especifica fila/columna con fallo</t>
-  </si>
-  <si>
     <t>AER25-125: CP7</t>
   </si>
   <si>
-    <t>Validar mapeo correcto de columnas específicas desde Excel</t>
-  </si>
-  <si>
-    <t>Archivo válido con todas las columnas requeridas</t>
-  </si>
-  <si>
-    <t>201/200, Todos los registros en BD coinciden con los datos de las columnas del archivo</t>
-  </si>
-  <si>
     <t>AER25-125: CP8</t>
   </si>
   <si>
-    <t>Validar que el endpoint elimina registros previos de la revisión antes de insertar</t>
-  </si>
-  <si>
-    <t>Registros previos para revisión, carga de nuevo archivo</t>
-  </si>
-  <si>
-    <t>Datos existentes ELIMINADOS, solo nuevos del archivo insertados; sin duplicados</t>
-  </si>
-  <si>
     <t>AER25-125: CP9</t>
   </si>
   <si>
-    <t>Validar que se procesa el checkbox de suplemento</t>
-  </si>
-  <si>
-    <t>Enviar petición con suplemento true/false</t>
-  </si>
-  <si>
-    <t>Indicador de suplemento guardado según valor de la petición</t>
-  </si>
-  <si>
     <t>AER25-125: CP10</t>
   </si>
   <si>
-    <t>Validar que el sistema calcula correctamente el número de "revisión" para nueva revisión</t>
-  </si>
-  <si>
-    <t>Revisión(es) previas existen, carga con "-1"</t>
-  </si>
-  <si>
-    <t>Nueva revisión = max (existente) + 1</t>
-  </si>
-  <si>
     <t>AER25-125: CP11</t>
   </si>
   <si>
-    <t>Validar estructura de respuesta exitosa</t>
-  </si>
-  <si>
-    <t>Archivo válido, carga exitosa</t>
-  </si>
-  <si>
-    <t>Respuesta incluye: estado 200/201, mensaje "Carga exitosa"</t>
-  </si>
-  <si>
-    <t>Media</t>
-  </si>
-  <si>
     <t>AER25-125: CP12</t>
   </si>
   <si>
-    <t>Validar estructura de respuesta de error en petición inválida</t>
-  </si>
-  <si>
-    <t>Cualquier error de validación conocido</t>
-  </si>
-  <si>
-    <t>Respuesta incluye: mensaje de error detallado con fila/columna, http 400, sin inserciones parciales</t>
-  </si>
-  <si>
     <t>AER25-125: CP13</t>
   </si>
   <si>
-    <t>Validar carga con archivo nulo o vacío</t>
-  </si>
-  <si>
-    <t>archivo=null o tamaño archivo=0</t>
-  </si>
-  <si>
-    <t>400, error "Archivo requerido" o "Archivo vacío"</t>
-  </si>
-  <si>
     <t>AER25-125: CP14</t>
   </si>
   <si>
-    <t>Validar carga con parámetro 'revision' ausente o inválido</t>
-  </si>
-  <si>
-    <t>parámetro revisión null/inválido</t>
-  </si>
-  <si>
-    <t>400, error "Parámetro de revisión inválido"</t>
-  </si>
-  <si>
     <t>AER25-125: CP15</t>
   </si>
   <si>
-    <t>Validar carga con caracteres no soportados/UTF-8 en campos de texto</t>
-  </si>
-  <si>
-    <t>Archivo contiene símbolos, caracteres acentuados</t>
-  </si>
-  <si>
-    <t>Se acepta si codificación válida; error si codificación incompatible</t>
-  </si>
-  <si>
     <t>AER25-125: CP16</t>
   </si>
   <si>
-    <t>Validar carga con máximos límites de columnas y filas</t>
-  </si>
-  <si>
-    <t>Archivo con datos en máximo permitido</t>
-  </si>
-  <si>
-    <t>El sistema procesa sin errores de tiempo de espera/memoria</t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
     <t>AER25-125: CP17</t>
   </si>
   <si>
-    <t>Validar carga con columnas extras (no usadas) en Excel</t>
-  </si>
-  <si>
-    <t>Archivo con columnas adicionales fuera del mapeo</t>
-  </si>
-  <si>
-    <t>Columnas extras ignoradas, columnas mapeadas válidamente procesadas</t>
-  </si>
-  <si>
     <t>AER25-125: CP18</t>
   </si>
   <si>
-    <t>Validar carga cuando todas las filas están vacías o sólo encabezados</t>
-  </si>
-  <si>
-    <t>Archivo solo encabezados o filas vacías</t>
-  </si>
-  <si>
-    <t>400, error "No se encontraron datos"</t>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Test Case ID</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Precondition</t>
+  </si>
+  <si>
+    <t>Expected Validation</t>
+  </si>
+  <si>
+    <t>Actual Result</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Validate successful upload with a valid .XLSX file (new revision)</t>
+  </si>
+  <si>
+    <t>Valid Excel file, revision="-1"</t>
+  </si>
+  <si>
+    <t>201/200, Message: "Upload successful"</t>
+  </si>
+  <si>
+    <t>Validate successful upload with a valid .XLSX file (existing revision)</t>
+  </si>
+  <si>
+    <t>Valid Excel file, valid existing revision</t>
+  </si>
+  <si>
+    <t>201/200, existing records deleted, new records inserted, message: "Upload successful"</t>
+  </si>
+  <si>
+    <t>Validate error response for an invalid file format (e.g., .CSV, .XLS, .TXT)</t>
+  </si>
+  <si>
+    <t>Invalid file type, e.g., .csv</t>
+  </si>
+  <si>
+    <t>400/415, Error message: "Invalid file type; only .XLSX is allowed"</t>
+  </si>
+  <si>
+    <t>Validate a file containing a numeric format error in one row</t>
+  </si>
+  <si>
+    <t>File with an invalid numeric value in a column</t>
+  </si>
+  <si>
+    <t>400, Message: "Error in row X, column 'Y': invalid format"; database NOT modified/rollback</t>
+  </si>
+  <si>
+    <t>Validate a file containing a date format error in one row</t>
+  </si>
+  <si>
+    <t>File with an invalid date value</t>
+  </si>
+  <si>
+    <t>400, "Error in row X, column 'Z': invalid format"; no database changes/rollback</t>
+  </si>
+  <si>
+    <t>Validate a complete rollback when a single error occurs in the file</t>
+  </si>
+  <si>
+    <t>File contains valid rows and 1 invalid row</t>
+  </si>
+  <si>
+    <t>400, database unchanged/rollback; error message specifies the failed row/column</t>
+  </si>
+  <si>
+    <t>Validate correct mapping of specific columns from Excel</t>
+  </si>
+  <si>
+    <t>Valid file with all required columns</t>
+  </si>
+  <si>
+    <t>201/200, all database records match the data in the file columns</t>
+  </si>
+  <si>
+    <t>Validate that the endpoint deletes previous records for the revision before inserting</t>
+  </si>
+  <si>
+    <t>Previous records exist for the revision; upload a new file</t>
+  </si>
+  <si>
+    <t>Existing data DELETED; only new records from the file inserted; no duplicates</t>
+  </si>
+  <si>
+    <t>Validate that the supplement checkbox is processed</t>
+  </si>
+  <si>
+    <t>Send request with supplement set to true/false</t>
+  </si>
+  <si>
+    <t>Supplement indicator saved according to the request value</t>
+  </si>
+  <si>
+    <t>Validate that the system correctly calculates the revision number for a new revision</t>
+  </si>
+  <si>
+    <t>Previous revision(s) exist; upload with "-1"</t>
+  </si>
+  <si>
+    <t>New revision = max(existing) + 1</t>
+  </si>
+  <si>
+    <t>Validate the successful response structure</t>
+  </si>
+  <si>
+    <t>Valid file, successful upload</t>
+  </si>
+  <si>
+    <t>Response includes: 200/201 status, message "Upload successful"</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Validate the error response structure for an invalid request</t>
+  </si>
+  <si>
+    <t>Any known validation error</t>
+  </si>
+  <si>
+    <t>Response includes: detailed error message with row/column, HTTP 400, no partial inserts</t>
+  </si>
+  <si>
+    <t>Validate upload with a null or empty file</t>
+  </si>
+  <si>
+    <t>file=null or file size=0</t>
+  </si>
+  <si>
+    <t>400, error "File required" or "Empty file"</t>
+  </si>
+  <si>
+    <t>Validate upload with a missing or invalid 'revision' parameter</t>
+  </si>
+  <si>
+    <t>revision parameter is null/invalid</t>
+  </si>
+  <si>
+    <t>400, error "Invalid revision parameter"</t>
+  </si>
+  <si>
+    <t>Validate upload with unsupported/UTF-8 characters in text fields</t>
+  </si>
+  <si>
+    <t>File contains symbols and accented characters</t>
+  </si>
+  <si>
+    <t>Accepted if encoding is valid; error if encoding is incompatible</t>
+  </si>
+  <si>
+    <t>Validate upload at the maximum column and row limits</t>
+  </si>
+  <si>
+    <t>File with data at the maximum allowed limit</t>
+  </si>
+  <si>
+    <t>The system processes the file without timeout or memory errors</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Validate upload with extra (unused) columns in Excel</t>
+  </si>
+  <si>
+    <t>File with additional columns outside the mapping</t>
+  </si>
+  <si>
+    <t>Extra columns ignored; mapped columns processed correctly</t>
+  </si>
+  <si>
+    <t>Validate upload when all rows are empty or the file contains only headers</t>
+  </si>
+  <si>
+    <t>File contains only headers or empty rows</t>
+  </si>
+  <si>
+    <t>400, error "No data found"</t>
   </si>
 </sst>
 </file>
@@ -360,6 +360,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -659,336 +663,336 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F15" s="2"/>
     </row>
     <row r="16" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F16" s="2"/>
     </row>
     <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F17" s="2"/>
     </row>
     <row r="18" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F18" s="2"/>
     </row>
     <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>78</v>
